--- a/output/mobilite_internationale_etablissements.xlsx
+++ b/output/mobilite_internationale_etablissements.xlsx
@@ -521,31 +521,19 @@
         </is>
       </c>
       <c r="D4">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>61</v>
-      </c>
-      <c r="I4">
-        <v>16.88</v>
-      </c>
-      <c r="J4">
-        <v>19.48</v>
-      </c>
-      <c r="K4">
-        <v>12.66</v>
-      </c>
-      <c r="L4">
-        <v>19.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -697,31 +685,19 @@
         </is>
       </c>
       <c r="D8">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>58</v>
-      </c>
-      <c r="I8">
-        <v>16.67</v>
-      </c>
-      <c r="J8">
-        <v>19.05</v>
-      </c>
-      <c r="K8">
-        <v>12.59</v>
-      </c>
-      <c r="L8">
-        <v>19.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -873,31 +849,19 @@
         </is>
       </c>
       <c r="D12">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>74</v>
-      </c>
-      <c r="I12">
-        <v>17.35</v>
-      </c>
-      <c r="J12">
-        <v>20.29</v>
-      </c>
-      <c r="K12">
-        <v>14.71</v>
-      </c>
-      <c r="L12">
-        <v>21.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1049,31 +1013,19 @@
         </is>
       </c>
       <c r="D16">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>73</v>
-      </c>
-      <c r="I16">
-        <v>17.58</v>
-      </c>
-      <c r="J16">
-        <v>20.61</v>
-      </c>
-      <c r="K16">
-        <v>14.24</v>
-      </c>
-      <c r="L16">
-        <v>22.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1225,31 +1177,19 @@
         </is>
       </c>
       <c r="D20">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>96</v>
-      </c>
-      <c r="I20">
-        <v>25.23</v>
-      </c>
-      <c r="J20">
-        <v>28.83</v>
-      </c>
-      <c r="K20">
-        <v>12.61</v>
-      </c>
-      <c r="L20">
-        <v>28.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1401,31 +1341,19 @@
         </is>
       </c>
       <c r="D24">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>91</v>
-      </c>
-      <c r="I24">
-        <v>24.76</v>
-      </c>
-      <c r="J24">
-        <v>28.53</v>
-      </c>
-      <c r="K24">
-        <v>12.54</v>
-      </c>
-      <c r="L24">
-        <v>28.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">

--- a/output/mobilite_internationale_etablissements.xlsx
+++ b/output/mobilite_internationale_etablissements.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Université Paris 1 - Panthéon Sorbonne  (Sciences Economiques)</t>
+          <t>Université Paris 1 - Panthéon Sorbonne (Sciences Economiques)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Université Paris 1 - Panthéon Sorbonne  (Sciences Economiques)</t>
+          <t>Université Paris 1 - Panthéon Sorbonne (Sciences Economiques)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Université Paris 1 - Panthéon Sorbonne  (Sciences Economiques)</t>
+          <t>Université Paris 1 - Panthéon Sorbonne (Sciences Economiques)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Université Paris 1 - Panthéon Sorbonne  (Sciences Economiques)</t>
+          <t>Université Paris 1 - Panthéon Sorbonne (Sciences Economiques)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Université Paris 1 - Panthéon Sorbonne  (Sciences Economiques)</t>
+          <t>Université Paris 1 - Panthéon Sorbonne (Sciences Economiques)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Université Paris 1 - Panthéon Sorbonne  (Sciences Economiques)</t>
+          <t>Université Paris 1 - Panthéon Sorbonne (Sciences Economiques)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">

--- a/output/mobilite_internationale_etablissements.xlsx
+++ b/output/mobilite_internationale_etablissements.xlsx
@@ -521,19 +521,31 @@
         </is>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I4">
+        <v>16.88</v>
+      </c>
+      <c r="J4">
+        <v>19.48</v>
+      </c>
+      <c r="K4">
+        <v>12.66</v>
+      </c>
+      <c r="L4">
+        <v>19.81</v>
       </c>
     </row>
     <row r="5">
@@ -685,19 +697,31 @@
         </is>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="I8">
+        <v>16.67</v>
+      </c>
+      <c r="J8">
+        <v>19.05</v>
+      </c>
+      <c r="K8">
+        <v>12.59</v>
+      </c>
+      <c r="L8">
+        <v>19.73</v>
       </c>
     </row>
     <row r="9">
@@ -849,19 +873,31 @@
         </is>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>74</v>
+      </c>
+      <c r="I12">
+        <v>17.35</v>
+      </c>
+      <c r="J12">
+        <v>20.29</v>
+      </c>
+      <c r="K12">
+        <v>14.71</v>
+      </c>
+      <c r="L12">
+        <v>21.76</v>
       </c>
     </row>
     <row r="13">
@@ -1013,19 +1049,31 @@
         </is>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>73</v>
+      </c>
+      <c r="I16">
+        <v>17.58</v>
+      </c>
+      <c r="J16">
+        <v>20.61</v>
+      </c>
+      <c r="K16">
+        <v>14.24</v>
+      </c>
+      <c r="L16">
+        <v>22.12</v>
       </c>
     </row>
     <row r="17">
@@ -1177,19 +1225,31 @@
         </is>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="I20">
+        <v>25.23</v>
+      </c>
+      <c r="J20">
+        <v>28.83</v>
+      </c>
+      <c r="K20">
+        <v>12.61</v>
+      </c>
+      <c r="L20">
+        <v>28.83</v>
       </c>
     </row>
     <row r="21">
@@ -1341,19 +1401,31 @@
         </is>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>91</v>
+      </c>
+      <c r="I24">
+        <v>24.76</v>
+      </c>
+      <c r="J24">
+        <v>28.53</v>
+      </c>
+      <c r="K24">
+        <v>12.54</v>
+      </c>
+      <c r="L24">
+        <v>28.53</v>
       </c>
     </row>
     <row r="25">
